--- a/data/trans_orig/P70C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023</t>
+          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>65425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99639</t>
+          <t>97598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62291</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86757</t>
+          <t>86356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132537</t>
+          <t>135786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177384</t>
+          <t>176812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48086</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>83381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>97455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136346</t>
+          <t>133180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56200</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>43647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60694</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>91376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72740</t>
+          <t>73955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81557</t>
+          <t>80942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116077</t>
+          <t>116906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35155</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64093</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24464</t>
+          <t>25314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44246</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102536</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81352</t>
+          <t>81562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208612</t>
+          <t>209319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629117</t>
+          <t>627549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81503</t>
+          <t>81336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113702</t>
+          <t>112360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305623</t>
+          <t>301483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878366</t>
+          <t>820674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>51110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184633</t>
+          <t>187483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89367</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88543</t>
+          <t>101360</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>259934</t>
+          <t>257983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109271</t>
+          <t>114204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56554</t>
+          <t>57265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55152</t>
+          <t>65646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157030</t>
+          <t>160331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43682</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174444</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58711</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87831</t>
+          <t>85638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98847</t>
+          <t>96755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241942</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126960</t>
+          <t>125597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60551</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89378</t>
+          <t>87256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67722</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>202595</t>
+          <t>203730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48533</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>31079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79578</t>
+          <t>81270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123525</t>
+          <t>121277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163923</t>
+          <t>163667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93945</t>
+          <t>93618</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188785</t>
+          <t>198219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>234881</t>
+          <t>231349</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336128</t>
+          <t>331073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78109</t>
+          <t>77159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53609</t>
+          <t>56174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81933</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123797</t>
+          <t>124239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32672</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41601</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39298</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56449</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89572</t>
+          <t>89628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31562</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>61328</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96617</t>
+          <t>97195</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143572</t>
+          <t>142811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67238</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71208</t>
+          <t>69381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81224</t>
+          <t>81739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130562</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37425</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55045</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151302</t>
+          <t>153335</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197200</t>
+          <t>193927</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128815</t>
+          <t>130465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>286923</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>301112</t>
+          <t>301204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>484112</t>
+          <t>488936</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>109031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50600</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>100415</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132411</t>
+          <t>133030</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>197633</t>
+          <t>197867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44109</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>72208</t>
+          <t>73545</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60225</t>
+          <t>59336</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>78386</t>
+          <t>76156</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>124497</t>
+          <t>122854</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46905</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>74342</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93513</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47989</t>
+          <t>48695</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78461</t>
+          <t>78822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82509</t>
+          <t>81960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>93081</t>
+          <t>96637</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147663</t>
+          <t>148795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>41298</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64996</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98690</t>
+          <t>96831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>618260</t>
+          <t>620219</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1204874</t>
+          <t>1241591</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>403588</t>
+          <t>408642</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>632967</t>
+          <t>622073</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1071068</t>
+          <t>1063850</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1855513</t>
+          <t>1751154</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>219954</t>
+          <t>209064</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>393699</t>
+          <t>392900</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207446</t>
+          <t>208720</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>278603</t>
+          <t>279100</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>439866</t>
+          <t>460512</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>654186</t>
+          <t>646695</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>127748</t>
+          <t>128208</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>234791</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>127096</t>
+          <t>130309</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>179826</t>
+          <t>179165</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267564</t>
+          <t>274116</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>392314</t>
+          <t>397369</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>204648</t>
+          <t>189660</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>357687</t>
+          <t>358699</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>179837</t>
+          <t>181263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>244441</t>
+          <t>244680</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>406047</t>
+          <t>400394</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>581424</t>
+          <t>583656</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>149249</t>
+          <t>148517</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>285778</t>
+          <t>281497</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>189651</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>253817</t>
+          <t>253211</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>356553</t>
+          <t>364324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>522052</t>
+          <t>526895</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>128038</t>
+          <t>129591</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111265</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>161090</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>179447</t>
+          <t>186803</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>277253</t>
+          <t>277502</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>93951</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97598</t>
+          <t>113754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>73652</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86356</t>
+          <t>95318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>154990</t>
+          <t>174001</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135786</t>
+          <t>151851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176812</t>
+          <t>198050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62358</t>
+          <t>64347</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83381</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>54647</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>44248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63454</t>
+          <t>65741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113485</t>
+          <t>118994</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97455</t>
+          <t>101781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133180</t>
+          <t>138756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43647</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>83621</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>69028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91376</t>
+          <t>100924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73955</t>
+          <t>81565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>44360</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>34247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>54997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>97053</t>
+          <t>105611</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80942</t>
+          <t>86987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116906</t>
+          <t>125559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65819</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33767</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25314</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82284</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>73314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102112</t>
+          <t>111829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>64289</t>
+          <t>68939</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>53957</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81562</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>332007</t>
+          <t>363887</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>332007</t>
+          <t>363887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332007</t>
+          <t>363887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>255514</t>
+          <t>276839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>255514</t>
+          <t>276839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255514</t>
+          <t>276839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>587521</t>
+          <t>640726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>587521</t>
+          <t>640726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>587521</t>
+          <t>640726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>398928</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209319</t>
+          <t>145016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627549</t>
+          <t>198219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97221</t>
+          <t>105721</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81336</t>
+          <t>89505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112360</t>
+          <t>123366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>496148</t>
+          <t>275403</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301483</t>
+          <t>246587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820674</t>
+          <t>308071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118791</t>
+          <t>136398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>113211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187483</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>87406</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>74627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>102315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>195749</t>
+          <t>223804</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101360</t>
+          <t>197426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>257983</t>
+          <t>251150</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>78890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114204</t>
+          <t>97566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>53056</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>42286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>66183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>118451</t>
+          <t>131946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>112479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160331</t>
+          <t>154911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>113249</t>
+          <t>124637</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48851</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171688</t>
+          <t>147859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71102</t>
+          <t>78260</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>64126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85638</t>
+          <t>92947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>184350</t>
+          <t>202897</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>175057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244724</t>
+          <t>230495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81126</t>
+          <t>91216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>72524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125597</t>
+          <t>115125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73678</t>
+          <t>82674</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87256</t>
+          <t>99216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154804</t>
+          <t>173890</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>150085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>203730</t>
+          <t>202854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58522</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31079</t>
+          <t>54737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81270</t>
+          <t>86992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>805363</t>
+          <t>627639</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>805363</t>
+          <t>627639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>805363</t>
+          <t>627639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>402662</t>
+          <t>449537</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402662</t>
+          <t>449537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402662</t>
+          <t>449537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1208025</t>
+          <t>1077176</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1208025</t>
+          <t>1077176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1208025</t>
+          <t>1077176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>143322</t>
+          <t>168071</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121277</t>
+          <t>145525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163667</t>
+          <t>193970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123004</t>
+          <t>106477</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93618</t>
+          <t>90600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>198219</t>
+          <t>122978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>266326</t>
+          <t>274548</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231349</t>
+          <t>246153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331073</t>
+          <t>305414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>68950</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>53229</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77159</t>
+          <t>89314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>40541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56174</t>
+          <t>64655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>102036</t>
+          <t>120645</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81677</t>
+          <t>100721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>141669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68034</t>
+          <t>82638</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71081</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>65450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>104405</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61328</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>118728</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>97195</t>
+          <t>115679</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142811</t>
+          <t>158978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64722</t>
+          <t>69722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>62865</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69381</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>102499</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81739</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126016</t>
+          <t>140809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38802</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>47178</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>62498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>174080</t>
+          <t>184854</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153335</t>
+          <t>161892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193927</t>
+          <t>208173</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>184680</t>
+          <t>121550</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130465</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>138982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>358759</t>
+          <t>306404</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>301204</t>
+          <t>276049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>488936</t>
+          <t>333988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>88666</t>
+          <t>96077</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73096</t>
+          <t>78928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109031</t>
+          <t>115841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80851</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44731</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>105124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>169517</t>
+          <t>185529</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133030</t>
+          <t>162736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>197867</t>
+          <t>210669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>68768</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44790</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>88197</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>45013</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59336</t>
+          <t>64589</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>102606</t>
+          <t>119250</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>76156</t>
+          <t>100552</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>122854</t>
+          <t>144571</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>69311</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48155</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76714</t>
+          <t>87386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>58481</t>
+          <t>66758</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>54996</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74342</t>
+          <t>83251</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>119919</t>
+          <t>136069</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>114956</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>141994</t>
+          <t>157276</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>62244</t>
+          <t>66943</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48695</t>
+          <t>51751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78822</t>
+          <t>84423</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>71388</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37016</t>
+          <t>58289</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>81960</t>
+          <t>85575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>125625</t>
+          <t>138330</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96637</t>
+          <t>116093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148795</t>
+          <t>160346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65137</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>79988</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>96831</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>479665</t>
+          <t>447709</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>479665</t>
+          <t>447709</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>479665</t>
+          <t>447709</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>951867</t>
+          <t>965570</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>951867</t>
+          <t>965570</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>951867</t>
+          <t>965570</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>797666</t>
+          <t>616559</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>620219</t>
+          <t>569631</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1241591</t>
+          <t>665218</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>478557</t>
+          <t>413798</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>408642</t>
+          <t>382251</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>622073</t>
+          <t>446128</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1276223</t>
+          <t>1030356</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1063850</t>
+          <t>974186</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1751154</t>
+          <t>1084283</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>365771</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>209064</t>
+          <t>327980</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>392900</t>
+          <t>407489</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>250568</t>
+          <t>283200</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208720</t>
+          <t>257127</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>279100</t>
+          <t>309662</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>580786</t>
+          <t>648971</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>460512</t>
+          <t>599128</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>646695</t>
+          <t>691590</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>224870</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>128208</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>232060</t>
+          <t>252073</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>153950</t>
+          <t>175524</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130309</t>
+          <t>152823</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>179165</t>
+          <t>198989</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>400395</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>274116</t>
+          <t>364678</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>397369</t>
+          <t>441219</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>338816</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>189660</t>
+          <t>302745</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>358699</t>
+          <t>378338</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>242881</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>181263</t>
+          <t>218355</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>268780</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>581697</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>400394</t>
+          <t>535008</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>583656</t>
+          <t>629366</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>264940</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>148517</t>
+          <t>234243</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>281497</t>
+          <t>304435</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>226395</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>189651</t>
+          <t>227281</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>253211</t>
+          <t>279162</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>465212</t>
+          <t>517910</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>364324</t>
+          <t>474301</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>526895</t>
+          <t>560037</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>120028</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63454</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>129591</t>
+          <t>146686</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>135805</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>111265</t>
+          <t>125897</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>161090</t>
+          <t>166887</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>265342</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>277502</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
